--- a/artfynd/A 52405-2025 artfynd.xlsx
+++ b/artfynd/A 52405-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>7190902</v>
       </c>
       <c r="B2" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508481.1595299988</v>
+        <v>508481</v>
       </c>
       <c r="R2" t="n">
-        <v>6399001.19997228</v>
+        <v>6399001</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1978-05-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1999-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -793,6 +778,314 @@
           <t>Äldre fynd i Östergötlands flora</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>88275524</v>
+      </c>
+      <c r="B3" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Salebo brant, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>508868</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6398746</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Åke Bruhn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Åke Bruhn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>88275539</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Salebo brant, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>508868</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6398746</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åke Bruhn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åke Bruhn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>88275555</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Salebo brant, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>508868</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6398746</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ydre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västra Ryd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-05-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Åke Bruhn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åke Bruhn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52405-2025 artfynd.xlsx
+++ b/artfynd/A 52405-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88275524</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88275539</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88275555</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,8 +1106,19 @@
           <t>Äldre fynd i Östergötlands flora</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7190902</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>